--- a/survey_templates/041_personal_space_boundary_assessment--survey_templates.xlsx
+++ b/survey_templates/041_personal_space_boundary_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[{1:_none,_'label':_'none',_'value':_1},_{2:_none,_'label':_'some',_'value':_2},_{3:_none,_'label':_'most',_'value':_3}]</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[{1: None, 'label': 'None', 'value': 1}, {2: None, 'label': 'Some', 'value': 2}, {3: None, 'label': 'Most', 'value': 3}]</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'counselor',_'value':_1}</t>
+          <t>counselor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Counselor', 'value': 1}</t>
+          <t>Counselor</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'educator',_'value':_2}</t>
+          <t>educator</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Educator', 'value': 2}</t>
+          <t>Educator</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hr',_'value':_3}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'HR', 'value': 3}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_4}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 4}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
